--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/66.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/66.xlsx
@@ -426,13 +426,13 @@
         <v>-1.497729830551522</v>
       </c>
       <c r="E2">
-        <v>-25.3575681460004</v>
+        <v>-28.65295226680415</v>
       </c>
       <c r="F2">
-        <v>-7.622104818621934</v>
+        <v>-7.988632964573494</v>
       </c>
       <c r="G2">
-        <v>-16.7571583446198</v>
+        <v>-16.76550422992431</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.397896346762986</v>
       </c>
       <c r="E3">
-        <v>-27.38086316178347</v>
+        <v>-29.22465852485051</v>
       </c>
       <c r="F3">
-        <v>-7.227339592124569</v>
+        <v>-8.673516089940776</v>
       </c>
       <c r="G3">
-        <v>-16.41574840424585</v>
+        <v>-15.96422971923573</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.444113589393419</v>
       </c>
       <c r="E4">
-        <v>-28.1228174001482</v>
+        <v>-28.56576102826046</v>
       </c>
       <c r="F4">
-        <v>-7.036621807257773</v>
+        <v>-8.334837412512218</v>
       </c>
       <c r="G4">
-        <v>-15.70181105070155</v>
+        <v>-17.57083746944403</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.630202451860524</v>
       </c>
       <c r="E5">
-        <v>-28.11302683934362</v>
+        <v>-29.12811598748098</v>
       </c>
       <c r="F5">
-        <v>-7.071233700039702</v>
+        <v>-7.982416918855394</v>
       </c>
       <c r="G5">
-        <v>-16.47279738025134</v>
+        <v>-16.92513211473689</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.921738387256469</v>
       </c>
       <c r="E6">
-        <v>-28.66598974347223</v>
+        <v>-29.70662854196087</v>
       </c>
       <c r="F6">
-        <v>-6.957352575072282</v>
+        <v>-8.438405048631818</v>
       </c>
       <c r="G6">
-        <v>-16.44660930976293</v>
+        <v>-17.23299298661587</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.277522811303347</v>
       </c>
       <c r="E7">
-        <v>-28.57286167550449</v>
+        <v>-30.60364905153325</v>
       </c>
       <c r="F7">
-        <v>-7.041794586704077</v>
+        <v>-7.470639184869306</v>
       </c>
       <c r="G7">
-        <v>-15.81370086883784</v>
+        <v>-16.59741128016781</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.658583590197007</v>
       </c>
       <c r="E8">
-        <v>-28.68688412254362</v>
+        <v>-31.00746439998223</v>
       </c>
       <c r="F8">
-        <v>-6.966737616327176</v>
+        <v>-8.045552542953825</v>
       </c>
       <c r="G8">
-        <v>-15.93030324854928</v>
+        <v>-17.14358673850954</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.026035971270489</v>
       </c>
       <c r="E9">
-        <v>-28.60409456073539</v>
+        <v>-32.99622527298281</v>
       </c>
       <c r="F9">
-        <v>-6.643420094425425</v>
+        <v>-8.153701048433831</v>
       </c>
       <c r="G9">
-        <v>-15.75002087011718</v>
+        <v>-17.72699093671315</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.341641235561624</v>
       </c>
       <c r="E10">
-        <v>-29.15212142819564</v>
+        <v>-32.37459711747589</v>
       </c>
       <c r="F10">
-        <v>-6.868290497358672</v>
+        <v>-7.43821716144195</v>
       </c>
       <c r="G10">
-        <v>-15.76521627414244</v>
+        <v>-17.67612605977502</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.581178777835719</v>
       </c>
       <c r="E11">
-        <v>-29.99089896931837</v>
+        <v>-31.97347394682447</v>
       </c>
       <c r="F11">
-        <v>-6.374668367987181</v>
+        <v>-7.592942061968554</v>
       </c>
       <c r="G11">
-        <v>-16.21057568917674</v>
+        <v>-17.49478265149759</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.727151411137394</v>
       </c>
       <c r="E12">
-        <v>-30.39799972565992</v>
+        <v>-32.53606438669339</v>
       </c>
       <c r="F12">
-        <v>-6.779490918900545</v>
+        <v>-7.095586741827893</v>
       </c>
       <c r="G12">
-        <v>-16.34280384383354</v>
+        <v>-17.60499071249993</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.772375235773261</v>
       </c>
       <c r="E13">
-        <v>-30.83279210055837</v>
+        <v>-32.71260241740841</v>
       </c>
       <c r="F13">
-        <v>-6.701136276881221</v>
+        <v>-7.310411698139508</v>
       </c>
       <c r="G13">
-        <v>-15.18276054723584</v>
+        <v>-18.06994690185395</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.725235355015698</v>
       </c>
       <c r="E14">
-        <v>-30.75690393313783</v>
+        <v>-32.37211324948269</v>
       </c>
       <c r="F14">
-        <v>-6.627177210630199</v>
+        <v>-8.154220899900574</v>
       </c>
       <c r="G14">
-        <v>-14.27770539970941</v>
+        <v>-17.18788018255222</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.599515580146114</v>
       </c>
       <c r="E15">
-        <v>-31.77155155505945</v>
+        <v>-33.94282125175416</v>
       </c>
       <c r="F15">
-        <v>-6.481873776594545</v>
+        <v>-7.230175217566162</v>
       </c>
       <c r="G15">
-        <v>-14.78010054856705</v>
+        <v>-16.14095657175864</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.415796017466548</v>
       </c>
       <c r="E16">
-        <v>-31.80639136983746</v>
+        <v>-33.6519030245534</v>
       </c>
       <c r="F16">
-        <v>-6.816526277659576</v>
+        <v>-6.809413062540379</v>
       </c>
       <c r="G16">
-        <v>-14.26411229972517</v>
+        <v>-17.14507482872945</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.200182423384964</v>
       </c>
       <c r="E17">
-        <v>-32.75661012781495</v>
+        <v>-33.25706537582462</v>
       </c>
       <c r="F17">
-        <v>-6.293095239621205</v>
+        <v>-6.641925471967729</v>
       </c>
       <c r="G17">
-        <v>-14.68543549887159</v>
+        <v>-15.74357358267945</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.974083796017889</v>
       </c>
       <c r="E18">
-        <v>-31.95336752223041</v>
+        <v>-35.47024157098632</v>
       </c>
       <c r="F18">
-        <v>-6.495931146226464</v>
+        <v>-7.0075881226365</v>
       </c>
       <c r="G18">
-        <v>-14.09288260807021</v>
+        <v>-16.14758593920103</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.757581371064935</v>
       </c>
       <c r="E19">
-        <v>-34.12610897297761</v>
+        <v>-34.61667856222854</v>
       </c>
       <c r="F19">
-        <v>-5.781247822574837</v>
+        <v>-6.779140523966754</v>
       </c>
       <c r="G19">
-        <v>-13.44167347140402</v>
+        <v>-15.80198815871989</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.566530934095454</v>
       </c>
       <c r="E20">
-        <v>-34.54595511941375</v>
+        <v>-35.05860554792608</v>
       </c>
       <c r="F20">
-        <v>-5.921072425996028</v>
+        <v>-6.343777392253577</v>
       </c>
       <c r="G20">
-        <v>-13.3799053127323</v>
+        <v>-15.34370933971858</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.405403324406353</v>
       </c>
       <c r="E21">
-        <v>-34.89970592347094</v>
+        <v>-33.81690250349688</v>
       </c>
       <c r="F21">
-        <v>-5.866539096503787</v>
+        <v>-6.026431629432468</v>
       </c>
       <c r="G21">
-        <v>-14.57193841087599</v>
+        <v>-15.06685338208764</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.278395150219917</v>
       </c>
       <c r="E22">
-        <v>-34.43857367950687</v>
+        <v>-34.81405889456387</v>
       </c>
       <c r="F22">
-        <v>-5.664984012057639</v>
+        <v>-6.32668405838176</v>
       </c>
       <c r="G22">
-        <v>-12.95851259212955</v>
+        <v>-14.71691547640452</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.183904745484783</v>
       </c>
       <c r="E23">
-        <v>-35.70056881596444</v>
+        <v>-37.57617897317236</v>
       </c>
       <c r="F23">
-        <v>-5.490880885949719</v>
+        <v>-6.486550460162838</v>
       </c>
       <c r="G23">
-        <v>-13.63985928011249</v>
+        <v>-14.61406675813598</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.112788977484519</v>
       </c>
       <c r="E24">
-        <v>-36.52356009669643</v>
+        <v>-38.95791601934076</v>
       </c>
       <c r="F24">
-        <v>-5.143905173230174</v>
+        <v>-6.535516271509352</v>
       </c>
       <c r="G24">
-        <v>-13.03416517879298</v>
+        <v>-14.1261585565582</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.060983657245068</v>
       </c>
       <c r="E25">
-        <v>-36.7772882311092</v>
+        <v>-37.57371548331219</v>
       </c>
       <c r="F25">
-        <v>-4.949034911453097</v>
+        <v>-6.718736396645978</v>
       </c>
       <c r="G25">
-        <v>-13.50197340312908</v>
+        <v>-15.4791636210034</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.020270675258777</v>
       </c>
       <c r="E26">
-        <v>-35.56547311513062</v>
+        <v>-36.52180531301846</v>
       </c>
       <c r="F26">
-        <v>-4.877839412024517</v>
+        <v>-6.181356868757375</v>
       </c>
       <c r="G26">
-        <v>-13.37200966162114</v>
+        <v>-15.07377407753749</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.98028862508045</v>
       </c>
       <c r="E27">
-        <v>-35.74814722812603</v>
+        <v>-36.9205714129489</v>
       </c>
       <c r="F27">
-        <v>-5.254618094513758</v>
+        <v>-5.716695969461526</v>
       </c>
       <c r="G27">
-        <v>-13.55139653748486</v>
+        <v>-14.89178676815267</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.936828693374004</v>
       </c>
       <c r="E28">
-        <v>-34.89967648838989</v>
+        <v>-38.50651546601917</v>
       </c>
       <c r="F28">
-        <v>-5.014298640375399</v>
+        <v>-6.446230891261664</v>
       </c>
       <c r="G28">
-        <v>-13.04839059297523</v>
+        <v>-13.81208544597477</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.880965682408593</v>
       </c>
       <c r="E29">
-        <v>-36.10315694795735</v>
+        <v>-36.95625805236634</v>
       </c>
       <c r="F29">
-        <v>-5.181353483306656</v>
+        <v>-5.491716290820113</v>
       </c>
       <c r="G29">
-        <v>-13.91708436357106</v>
+        <v>-14.68398051410708</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.804202578848797</v>
       </c>
       <c r="E30">
-        <v>-36.85871245800411</v>
+        <v>-37.02339720800406</v>
       </c>
       <c r="F30">
-        <v>-5.071414202362765</v>
+        <v>-6.227109736727941</v>
       </c>
       <c r="G30">
-        <v>-13.4754079304492</v>
+        <v>-15.67280239541368</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.701059377609222</v>
       </c>
       <c r="E31">
-        <v>-35.68426178106282</v>
+        <v>-37.56795073590042</v>
       </c>
       <c r="F31">
-        <v>-5.225967270797543</v>
+        <v>-6.000937131605724</v>
       </c>
       <c r="G31">
-        <v>-13.93073539810225</v>
+        <v>-15.53416999041116</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.565006257393873</v>
       </c>
       <c r="E32">
-        <v>-35.57208921565582</v>
+        <v>-36.64456318641839</v>
       </c>
       <c r="F32">
-        <v>-5.03129338855398</v>
+        <v>-6.005757140559364</v>
       </c>
       <c r="G32">
-        <v>-14.01791364906065</v>
+        <v>-14.51935701607574</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.392980951719321</v>
       </c>
       <c r="E33">
-        <v>-35.11630283525781</v>
+        <v>-38.3947708414059</v>
       </c>
       <c r="F33">
-        <v>-5.576967180248219</v>
+        <v>-6.575595117111378</v>
       </c>
       <c r="G33">
-        <v>-13.99208146221771</v>
+        <v>-15.18812859682776</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.184842470929776</v>
       </c>
       <c r="E34">
-        <v>-35.44890340146218</v>
+        <v>-37.44925263944837</v>
       </c>
       <c r="F34">
-        <v>-5.013707126215983</v>
+        <v>-6.121797252616007</v>
       </c>
       <c r="G34">
-        <v>-13.25400526587382</v>
+        <v>-14.93617952856153</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.943506885882593</v>
       </c>
       <c r="E35">
-        <v>-34.85632314247746</v>
+        <v>-35.29630062011469</v>
       </c>
       <c r="F35">
-        <v>-5.334635627744293</v>
+        <v>-5.742348837879813</v>
       </c>
       <c r="G35">
-        <v>-14.22754897951669</v>
+        <v>-15.18655774296938</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.6760845520067534</v>
       </c>
       <c r="E36">
-        <v>-34.20886909970479</v>
+        <v>-36.2692025043966</v>
       </c>
       <c r="F36">
-        <v>-4.885972533753256</v>
+        <v>-6.065938757199021</v>
       </c>
       <c r="G36">
-        <v>-13.95780903952241</v>
+        <v>-14.96831002829293</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.3923975510681547</v>
       </c>
       <c r="E37">
-        <v>-34.92200865795871</v>
+        <v>-36.97281868181239</v>
       </c>
       <c r="F37">
-        <v>-5.352107863256379</v>
+        <v>-5.648619578833403</v>
       </c>
       <c r="G37">
-        <v>-14.06500946990232</v>
+        <v>-15.48777103940551</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.1034738204250435</v>
       </c>
       <c r="E38">
-        <v>-34.11453645765101</v>
+        <v>-36.30582200945963</v>
       </c>
       <c r="F38">
-        <v>-5.178670685485901</v>
+        <v>-5.874576404024642</v>
       </c>
       <c r="G38">
-        <v>-13.58721167440146</v>
+        <v>-14.85862668875856</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.1799071741493479</v>
       </c>
       <c r="E39">
-        <v>-33.57024331701009</v>
+        <v>-35.40064798243644</v>
       </c>
       <c r="F39">
-        <v>-5.126688706223432</v>
+        <v>-6.311086138820597</v>
       </c>
       <c r="G39">
-        <v>-13.92776749402629</v>
+        <v>-14.90343326735983</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.4486866145208065</v>
       </c>
       <c r="E40">
-        <v>-33.58076522636691</v>
+        <v>-35.81416785068386</v>
       </c>
       <c r="F40">
-        <v>-4.989569072505812</v>
+        <v>-5.559188497641495</v>
       </c>
       <c r="G40">
-        <v>-13.78006088370063</v>
+        <v>-14.15254360450619</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.6966474526405603</v>
       </c>
       <c r="E41">
-        <v>-33.16637815534702</v>
+        <v>-35.96997905586577</v>
       </c>
       <c r="F41">
-        <v>-5.238281376143043</v>
+        <v>-5.296949761780497</v>
       </c>
       <c r="G41">
-        <v>-14.09785173692466</v>
+        <v>-15.35841478300403</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.9193978958621883</v>
       </c>
       <c r="E42">
-        <v>-32.24455066516062</v>
+        <v>-33.8908932403082</v>
       </c>
       <c r="F42">
-        <v>-5.081751050872838</v>
+        <v>-5.848845142163539</v>
       </c>
       <c r="G42">
-        <v>-14.17082940279235</v>
+        <v>-15.11270609307932</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.115046855015629</v>
       </c>
       <c r="E43">
-        <v>-32.49649458081436</v>
+        <v>-34.78059800012119</v>
       </c>
       <c r="F43">
-        <v>-4.915834100641825</v>
+        <v>-5.625630503764884</v>
       </c>
       <c r="G43">
-        <v>-13.44901295086459</v>
+        <v>-14.55720482795346</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.282980191956608</v>
       </c>
       <c r="E44">
-        <v>-32.18718169219445</v>
+        <v>-33.72202870879918</v>
       </c>
       <c r="F44">
-        <v>-4.748871112653663</v>
+        <v>-5.823024400918214</v>
       </c>
       <c r="G44">
-        <v>-14.32596984312645</v>
+        <v>-15.1366165082367</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.423909344037255</v>
       </c>
       <c r="E45">
-        <v>-31.50349759312342</v>
+        <v>-33.36499702532344</v>
       </c>
       <c r="F45">
-        <v>-5.107956632655615</v>
+        <v>-5.834020862942069</v>
       </c>
       <c r="G45">
-        <v>-14.39607892128436</v>
+        <v>-15.19597293448307</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.539289454843866</v>
       </c>
       <c r="E46">
-        <v>-30.88317590236771</v>
+        <v>-34.21734187457314</v>
       </c>
       <c r="F46">
-        <v>-4.676007179043167</v>
+        <v>-5.842544368178964</v>
       </c>
       <c r="G46">
-        <v>-13.39435253346568</v>
+        <v>-14.49808179516762</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.631699627015441</v>
       </c>
       <c r="E47">
-        <v>-30.77522840320987</v>
+        <v>-33.84527792162894</v>
       </c>
       <c r="F47">
-        <v>-4.94077588510408</v>
+        <v>-5.632230598167478</v>
       </c>
       <c r="G47">
-        <v>-14.52704741336347</v>
+        <v>-15.30389340851777</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.704381522195119</v>
       </c>
       <c r="E48">
-        <v>-30.99018827164297</v>
+        <v>-34.29331381876283</v>
       </c>
       <c r="F48">
-        <v>-4.851595029446812</v>
+        <v>-5.475727987750794</v>
       </c>
       <c r="G48">
-        <v>-13.87169678422766</v>
+        <v>-14.27117038281489</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.758527104644975</v>
       </c>
       <c r="E49">
-        <v>-29.69582813145258</v>
+        <v>-32.10194222594806</v>
       </c>
       <c r="F49">
-        <v>-4.690763358910274</v>
+        <v>-5.711590101590149</v>
       </c>
       <c r="G49">
-        <v>-14.51194967043162</v>
+        <v>-14.04760924254791</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.796735604156235</v>
       </c>
       <c r="E50">
-        <v>-30.02245111196681</v>
+        <v>-32.77622521297917</v>
       </c>
       <c r="F50">
-        <v>-4.767451150453598</v>
+        <v>-5.293259726997523</v>
       </c>
       <c r="G50">
-        <v>-14.77266175274031</v>
+        <v>-15.32274862063669</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.821024000835975</v>
       </c>
       <c r="E51">
-        <v>-29.29127237750334</v>
+        <v>-32.02678087860576</v>
       </c>
       <c r="F51">
-        <v>-4.905983449847791</v>
+        <v>-5.191937389939538</v>
       </c>
       <c r="G51">
-        <v>-14.28239644273856</v>
+        <v>-14.23005506248991</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.831005179995686</v>
       </c>
       <c r="E52">
-        <v>-28.98114889203605</v>
+        <v>-32.52186082796833</v>
       </c>
       <c r="F52">
-        <v>-5.020772038304758</v>
+        <v>-6.074371199345778</v>
       </c>
       <c r="G52">
-        <v>-14.80587480086305</v>
+        <v>-14.6272692137466</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.829518523079173</v>
       </c>
       <c r="E53">
-        <v>-29.29704618186312</v>
+        <v>-31.59291457664187</v>
       </c>
       <c r="F53">
-        <v>-4.860746474079178</v>
+        <v>-5.851748866959498</v>
       </c>
       <c r="G53">
-        <v>-14.7325131117128</v>
+        <v>-15.5975834902159</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.818304456812408</v>
       </c>
       <c r="E54">
-        <v>-29.31804924431069</v>
+        <v>-29.28281771653102</v>
       </c>
       <c r="F54">
-        <v>-4.906205168675953</v>
+        <v>-5.364218462391745</v>
       </c>
       <c r="G54">
-        <v>-14.71183378900174</v>
+        <v>-14.47369135090704</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.797706866198775</v>
       </c>
       <c r="E55">
-        <v>-28.91265119419603</v>
+        <v>-31.82757783548235</v>
       </c>
       <c r="F55">
-        <v>-5.155372787763872</v>
+        <v>-5.638775262863032</v>
       </c>
       <c r="G55">
-        <v>-13.78655948459422</v>
+        <v>-14.92762507888805</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.773108155203062</v>
       </c>
       <c r="E56">
-        <v>-27.511061317978</v>
+        <v>-30.83641487976451</v>
       </c>
       <c r="F56">
-        <v>-5.013273190795152</v>
+        <v>-5.675799139754175</v>
       </c>
       <c r="G56">
-        <v>-14.47436835746982</v>
+        <v>-14.21872472038176</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.747875934045692</v>
       </c>
       <c r="E57">
-        <v>-28.70944045157583</v>
+        <v>-32.01872245910911</v>
       </c>
       <c r="F57">
-        <v>-5.063586735875705</v>
+        <v>-5.711529920765362</v>
       </c>
       <c r="G57">
-        <v>-14.63705187581514</v>
+        <v>-16.02893433180078</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.725598549893213</v>
       </c>
       <c r="E58">
-        <v>-26.90601190581317</v>
+        <v>-30.70326642275398</v>
       </c>
       <c r="F58">
-        <v>-4.878209207355772</v>
+        <v>-5.670548362791536</v>
       </c>
       <c r="G58">
-        <v>-15.01377209491097</v>
+        <v>-14.5381228434651</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.71415057628481</v>
       </c>
       <c r="E59">
-        <v>-27.50168737678213</v>
+        <v>-29.4157057862861</v>
       </c>
       <c r="F59">
-        <v>-5.160432728163701</v>
+        <v>-5.829205605106175</v>
       </c>
       <c r="G59">
-        <v>-14.70951309657871</v>
+        <v>-16.01426530451627</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.716561602786059</v>
       </c>
       <c r="E60">
-        <v>-27.46065940227263</v>
+        <v>-28.65094162434474</v>
       </c>
       <c r="F60">
-        <v>-5.029624954372064</v>
+        <v>-6.526835187533871</v>
       </c>
       <c r="G60">
-        <v>-14.35940304252755</v>
+        <v>-16.36588827787888</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.736482693679518</v>
       </c>
       <c r="E61">
-        <v>-26.83515034454114</v>
+        <v>-30.07364777486053</v>
       </c>
       <c r="F61">
-        <v>-5.192576415276418</v>
+        <v>-6.16060636200033</v>
       </c>
       <c r="G61">
-        <v>-14.68925421315114</v>
+        <v>-15.40715263443318</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.778934216217155</v>
       </c>
       <c r="E62">
-        <v>-26.41658802048618</v>
+        <v>-28.29020338489372</v>
       </c>
       <c r="F62">
-        <v>-4.891597065311939</v>
+        <v>-5.824499622978446</v>
       </c>
       <c r="G62">
-        <v>-14.17400752651005</v>
+        <v>-15.96263569155857</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.842632975564313</v>
       </c>
       <c r="E63">
-        <v>-25.91976913710467</v>
+        <v>-27.04321108282356</v>
       </c>
       <c r="F63">
-        <v>-4.770368336749838</v>
+        <v>-6.170104638228177</v>
       </c>
       <c r="G63">
-        <v>-15.07673039470406</v>
+        <v>-16.83896854598627</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>1.931062726371043</v>
       </c>
       <c r="E64">
-        <v>-26.18255195529577</v>
+        <v>-28.79991936224908</v>
       </c>
       <c r="F64">
-        <v>-5.508609681820106</v>
+        <v>-6.296640761239395</v>
       </c>
       <c r="G64">
-        <v>-15.18486274365327</v>
+        <v>-16.04863538830498</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>2.047054018724316</v>
       </c>
       <c r="E65">
-        <v>-26.50473929551949</v>
+        <v>-29.4696625540875</v>
       </c>
       <c r="F65">
-        <v>-4.940862197076472</v>
+        <v>-6.071543492433761</v>
       </c>
       <c r="G65">
-        <v>-15.0762536761464</v>
+        <v>-16.73989716017805</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>2.185972591332194</v>
       </c>
       <c r="E66">
-        <v>-25.37166981406029</v>
+        <v>-30.60805525674271</v>
       </c>
       <c r="F66">
-        <v>-5.150555154369105</v>
+        <v>-6.240381192299324</v>
       </c>
       <c r="G66">
-        <v>-15.28951736451348</v>
+        <v>-16.40514141633802</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>2.34968166213427</v>
       </c>
       <c r="E67">
-        <v>-26.16678833727507</v>
+        <v>-29.87672708263699</v>
       </c>
       <c r="F67">
-        <v>-5.338281318761635</v>
+        <v>-6.412699877767023</v>
       </c>
       <c r="G67">
-        <v>-15.18633593641825</v>
+        <v>-15.74564598418704</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>2.535308884911412</v>
       </c>
       <c r="E68">
-        <v>-26.97598588617969</v>
+        <v>-30.01665240099999</v>
       </c>
       <c r="F68">
-        <v>-5.115240096160721</v>
+        <v>-6.103027566032697</v>
       </c>
       <c r="G68">
-        <v>-14.63214068150763</v>
+        <v>-15.78945774385375</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>2.734874316942728</v>
       </c>
       <c r="E69">
-        <v>-26.1413020855599</v>
+        <v>-29.53472314015569</v>
       </c>
       <c r="F69">
-        <v>-5.300060952051378</v>
+        <v>-6.30151461619416</v>
       </c>
       <c r="G69">
-        <v>-14.78835373859645</v>
+        <v>-17.4047142942834</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>2.947409673710328</v>
       </c>
       <c r="E70">
-        <v>-26.67125581325554</v>
+        <v>-28.39856523942327</v>
       </c>
       <c r="F70">
-        <v>-5.366541758969695</v>
+        <v>-6.295905921694631</v>
       </c>
       <c r="G70">
-        <v>-15.0597141906322</v>
+        <v>-16.99350812230499</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>3.166130529722688</v>
       </c>
       <c r="E71">
-        <v>-26.38136554965452</v>
+        <v>-28.35222536490278</v>
       </c>
       <c r="F71">
-        <v>-5.294743659440289</v>
+        <v>-7.367134896986324</v>
       </c>
       <c r="G71">
-        <v>-15.15305998793026</v>
+        <v>-15.27610965507944</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>3.382903350090707</v>
       </c>
       <c r="E72">
-        <v>-26.63649977524667</v>
+        <v>-29.72086832847799</v>
       </c>
       <c r="F72">
-        <v>-5.412586424755181</v>
+        <v>-6.127384567085677</v>
       </c>
       <c r="G72">
-        <v>-14.90770718165103</v>
+        <v>-16.20152134712684</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>3.595509978384105</v>
       </c>
       <c r="E73">
-        <v>-26.32294370648156</v>
+        <v>-27.46886952564854</v>
       </c>
       <c r="F73">
-        <v>-5.646782479971494</v>
+        <v>-6.429487160470681</v>
       </c>
       <c r="G73">
-        <v>-15.00796208748955</v>
+        <v>-15.76907637024123</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>3.795507063722867</v>
       </c>
       <c r="E74">
-        <v>-26.90376578270536</v>
+        <v>-28.39016944861304</v>
       </c>
       <c r="F74">
-        <v>-5.74337428746006</v>
+        <v>-6.656933857001869</v>
       </c>
       <c r="G74">
-        <v>-14.40263876727043</v>
+        <v>-14.74910722122839</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>3.977189636956751</v>
       </c>
       <c r="E75">
-        <v>-26.71943424822314</v>
+        <v>-28.45835468174654</v>
       </c>
       <c r="F75">
-        <v>-5.51919596401186</v>
+        <v>-6.972705416143032</v>
       </c>
       <c r="G75">
-        <v>-14.49913785919465</v>
+        <v>-15.83403423954004</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>4.138980100014495</v>
       </c>
       <c r="E76">
-        <v>-28.31669042936458</v>
+        <v>-30.783572116569</v>
       </c>
       <c r="F76">
-        <v>-5.632649488382111</v>
+        <v>-6.961652732559179</v>
       </c>
       <c r="G76">
-        <v>-14.21190499657086</v>
+        <v>-15.92804711176426</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>4.27307063393697</v>
       </c>
       <c r="E77">
-        <v>-26.6191647767453</v>
+        <v>-30.15264247545033</v>
       </c>
       <c r="F77">
-        <v>-5.841225141151402</v>
+        <v>-6.506755380232014</v>
       </c>
       <c r="G77">
-        <v>-14.24977267172181</v>
+        <v>-16.57426725630277</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>4.378253815904906</v>
       </c>
       <c r="E78">
-        <v>-27.29597238803569</v>
+        <v>-29.77701687769909</v>
       </c>
       <c r="F78">
-        <v>-5.877064406017797</v>
+        <v>-6.778549405733816</v>
       </c>
       <c r="G78">
-        <v>-13.89866283291779</v>
+        <v>-15.21934042017201</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>4.454409740587048</v>
       </c>
       <c r="E79">
-        <v>-27.71573475770268</v>
+        <v>-30.53501776371</v>
       </c>
       <c r="F79">
-        <v>-5.781209021779909</v>
+        <v>-6.57930336451238</v>
       </c>
       <c r="G79">
-        <v>-14.74865698703505</v>
+        <v>-14.86596285767359</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>4.495966090191754</v>
       </c>
       <c r="E80">
-        <v>-28.27531829083051</v>
+        <v>-31.91828316985599</v>
       </c>
       <c r="F80">
-        <v>-6.144323489630739</v>
+        <v>-6.665781626024951</v>
       </c>
       <c r="G80">
-        <v>-13.91219468780956</v>
+        <v>-13.97025006965899</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>4.506049303322421</v>
       </c>
       <c r="E81">
-        <v>-28.72652185553276</v>
+        <v>-31.05294386444127</v>
       </c>
       <c r="F81">
-        <v>-5.93992486121342</v>
+        <v>-6.938651383769815</v>
       </c>
       <c r="G81">
-        <v>-13.73612497857619</v>
+        <v>-15.40825008027944</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>4.484670345811047</v>
       </c>
       <c r="E82">
-        <v>-28.31227969568111</v>
+        <v>-31.63408519808261</v>
       </c>
       <c r="F82">
-        <v>-6.128923533309005</v>
+        <v>-7.038577288136862</v>
       </c>
       <c r="G82">
-        <v>-14.34656474692625</v>
+        <v>-15.52051399006167</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>4.427779014114094</v>
       </c>
       <c r="E83">
-        <v>-29.68853728830023</v>
+        <v>-33.36632839668169</v>
       </c>
       <c r="F83">
-        <v>-6.226246617004027</v>
+        <v>-6.874056374670308</v>
       </c>
       <c r="G83">
-        <v>-13.68134041571956</v>
+        <v>-13.9940280629948</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>4.33820744068028</v>
       </c>
       <c r="E84">
-        <v>-31.46834078516487</v>
+        <v>-33.68835724031515</v>
       </c>
       <c r="F84">
-        <v>-6.242935314014449</v>
+        <v>-6.722406239178531</v>
       </c>
       <c r="G84">
-        <v>-13.42432621277824</v>
+        <v>-15.28857220376202</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>4.21367881014253</v>
       </c>
       <c r="E85">
-        <v>-31.50674450898692</v>
+        <v>-34.8870488386195</v>
       </c>
       <c r="F85">
-        <v>-5.817484597626008</v>
+        <v>-6.801460483286</v>
       </c>
       <c r="G85">
-        <v>-14.33215394219381</v>
+        <v>-15.30345972705212</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>4.050008685675278</v>
       </c>
       <c r="E86">
-        <v>-32.01773525177543</v>
+        <v>-35.57219789903201</v>
       </c>
       <c r="F86">
-        <v>-6.01650971187224</v>
+        <v>-6.64318214261163</v>
       </c>
       <c r="G86">
-        <v>-14.28230540273623</v>
+        <v>-14.48539578466113</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.848005529871588</v>
       </c>
       <c r="E87">
-        <v>-32.63818600404036</v>
+        <v>-35.43440096345261</v>
       </c>
       <c r="F87">
-        <v>-6.353912318259431</v>
+        <v>-6.780005623323063</v>
       </c>
       <c r="G87">
-        <v>-13.08593880048164</v>
+        <v>-15.53237898527442</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.603041909274991</v>
       </c>
       <c r="E88">
-        <v>-33.12210552921103</v>
+        <v>-35.85801253602612</v>
       </c>
       <c r="F88">
-        <v>-6.098415814406938</v>
+        <v>-7.213155526019414</v>
       </c>
       <c r="G88">
-        <v>-13.68895632573266</v>
+        <v>-15.98095459530012</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.310774074315749</v>
       </c>
       <c r="E89">
-        <v>-34.72071345984376</v>
+        <v>-36.50940861542246</v>
       </c>
       <c r="F89">
-        <v>-6.020036624945925</v>
+        <v>-6.50843410850238</v>
       </c>
       <c r="G89">
-        <v>-13.81271279435446</v>
+        <v>-15.07945993950119</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.96781695455399</v>
       </c>
       <c r="E90">
-        <v>-35.7846693709979</v>
+        <v>-37.95385370541207</v>
       </c>
       <c r="F90">
-        <v>-6.202553188729617</v>
+        <v>-7.220511048143672</v>
       </c>
       <c r="G90">
-        <v>-13.35869795800773</v>
+        <v>-15.27091706440109</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.569116580217649</v>
       </c>
       <c r="E91">
-        <v>-37.68715828567834</v>
+        <v>-40.1849400152741</v>
       </c>
       <c r="F91">
-        <v>-6.370444228384225</v>
+        <v>-6.991814411718724</v>
       </c>
       <c r="G91">
-        <v>-13.19324351304604</v>
+        <v>-14.84278076253484</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.110276723094369</v>
       </c>
       <c r="E92">
-        <v>-38.41966386302607</v>
+        <v>-40.22082817178489</v>
       </c>
       <c r="F92">
-        <v>-5.952191455381456</v>
+        <v>-6.236020062134683</v>
       </c>
       <c r="G92">
-        <v>-13.46253652939251</v>
+        <v>-14.95467058067113</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.587603368280756</v>
       </c>
       <c r="E93">
-        <v>-39.63199296080452</v>
+        <v>-41.63237389810877</v>
       </c>
       <c r="F93">
-        <v>-6.200083399354488</v>
+        <v>-6.59706581413347</v>
       </c>
       <c r="G93">
-        <v>-13.82866962385375</v>
+        <v>-14.44543750000213</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.001462539156199</v>
       </c>
       <c r="E94">
-        <v>-40.40439439415982</v>
+        <v>-43.46076112836471</v>
       </c>
       <c r="F94">
-        <v>-6.527032754846822</v>
+        <v>-6.273523801918205</v>
       </c>
       <c r="G94">
-        <v>-13.84660947013106</v>
+        <v>-15.55428983092608</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.3537420734114153</v>
       </c>
       <c r="E95">
-        <v>-41.86687639612197</v>
+        <v>-43.47992110189116</v>
       </c>
       <c r="F95">
-        <v>-6.355578772808953</v>
+        <v>-6.937914168666178</v>
       </c>
       <c r="G95">
-        <v>-14.42451981801224</v>
+        <v>-15.48258838036378</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.3576881606868857</v>
       </c>
       <c r="E96">
-        <v>-44.23384409705816</v>
+        <v>-46.99722309144079</v>
       </c>
       <c r="F96">
-        <v>-6.454917122281371</v>
+        <v>-6.619463770969051</v>
       </c>
       <c r="G96">
-        <v>-14.71171295408956</v>
+        <v>-15.12121916093355</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.115286468965695</v>
       </c>
       <c r="E97">
-        <v>-45.38675055890796</v>
+        <v>-47.27499515859728</v>
       </c>
       <c r="F97">
-        <v>-6.238772147089238</v>
+        <v>-6.955300488132352</v>
       </c>
       <c r="G97">
-        <v>-15.08265792649212</v>
+        <v>-16.20886248186017</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.928330485880653</v>
       </c>
       <c r="E98">
-        <v>-47.45774625565083</v>
+        <v>-49.51325909976146</v>
       </c>
       <c r="F98">
-        <v>-6.515196532761307</v>
+        <v>-6.699948497444641</v>
       </c>
       <c r="G98">
-        <v>-14.71029769587152</v>
+        <v>-15.88273567496826</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.759163545340546</v>
       </c>
       <c r="E99">
-        <v>-48.68673334506649</v>
+        <v>-49.94778203045647</v>
       </c>
       <c r="F99">
-        <v>-6.516502694215065</v>
+        <v>-6.775144438015622</v>
       </c>
       <c r="G99">
-        <v>-15.14542421464393</v>
+        <v>-16.64149781511429</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.638336784041718</v>
       </c>
       <c r="E100">
-        <v>-50.38743119372814</v>
+        <v>-51.86881957467233</v>
       </c>
       <c r="F100">
-        <v>-6.542037180616174</v>
+        <v>-6.015464465968051</v>
       </c>
       <c r="G100">
-        <v>-14.88832228224583</v>
+        <v>-16.04827784938674</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.486906494494812</v>
       </c>
       <c r="E101">
-        <v>-52.30150507703871</v>
+        <v>-53.19936675065802</v>
       </c>
       <c r="F101">
-        <v>-6.413487375533475</v>
+        <v>-5.968159962126832</v>
       </c>
       <c r="G101">
-        <v>-15.46415195225558</v>
+        <v>-16.90388503346584</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.407540619742334</v>
       </c>
       <c r="E102">
-        <v>-54.31870137045195</v>
+        <v>-56.4142481890274</v>
       </c>
       <c r="F102">
-        <v>-6.477070792479496</v>
+        <v>-6.126996163209916</v>
       </c>
       <c r="G102">
-        <v>-15.8626125239078</v>
+        <v>-16.33461686471493</v>
       </c>
     </row>
   </sheetData>
